--- a/e2e/expectedData/moju_Expat_Local.xlsx
+++ b/e2e/expectedData/moju_Expat_Local.xlsx
@@ -80,7 +80,7 @@
     <t>Basic Salary - Expat</t>
   </si>
   <si>
-    <t>2,280.00</t>
+    <t>1,830.00</t>
   </si>
   <si>
     <t>Position Allowance - Expat</t>
@@ -170,15 +170,12 @@
     <t>Potongan Karyawan</t>
   </si>
   <si>
-    <t>2,450.00</t>
+    <t>1,130.00</t>
   </si>
   <si>
     <t>Potongan Donasi THR</t>
   </si>
   <si>
-    <t>1,000.00</t>
-  </si>
-  <si>
     <t>Potongan Biaya Housing</t>
   </si>
   <si>
@@ -197,13 +194,16 @@
     <t>TL20000002</t>
   </si>
   <si>
+    <t>2,737.72</t>
+  </si>
+  <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>5,068.86</t>
-  </si>
-  <si>
-    <t>DILI, 26 Agustus 2026</t>
+    <t>4,984.93</t>
+  </si>
+  <si>
+    <t>DILI, 09 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -708,7 +708,9 @@
       <c r="C6" s="3">
         <v>51111010</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4">
+        <v>300.0</v>
+      </c>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5">
@@ -721,7 +723,9 @@
       <c r="C7" s="3">
         <v>51111010</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="4">
+        <v>230.0</v>
+      </c>
       <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5">
@@ -734,7 +738,9 @@
       <c r="C8" s="3">
         <v>51111010</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="4">
+        <v>10.0</v>
+      </c>
       <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5">
@@ -747,7 +753,9 @@
       <c r="C9" s="3">
         <v>51141004</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4">
+        <v>36.0</v>
+      </c>
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5">
@@ -760,7 +768,9 @@
       <c r="C10" s="3">
         <v>51111010</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="4">
+        <v>43.0</v>
+      </c>
       <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:5">
@@ -773,7 +783,9 @@
       <c r="C11" s="3">
         <v>51111010</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4">
+        <v>817.58</v>
+      </c>
       <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:5">
@@ -799,7 +811,9 @@
       <c r="C13" s="3">
         <v>51141009</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="4">
+        <v>60.0</v>
+      </c>
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5">
@@ -864,7 +878,9 @@
       <c r="C18" s="3">
         <v>51141009</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4">
+        <v>347.5</v>
+      </c>
       <c r="E18" s="4"/>
     </row>
     <row r="19" spans="1:5">
@@ -893,7 +909,7 @@
         <v>51111010</v>
       </c>
       <c r="D20" s="4">
-        <v>510.0</v>
+        <v>230.0</v>
       </c>
       <c r="E20" s="4"/>
     </row>
@@ -908,7 +924,7 @@
         <v>51111010</v>
       </c>
       <c r="D21" s="4">
-        <v>120.0</v>
+        <v>100.0</v>
       </c>
       <c r="E21" s="4"/>
     </row>
@@ -938,7 +954,7 @@
         <v>51141004</v>
       </c>
       <c r="D23" s="4">
-        <v>103.64</v>
+        <v>59.38</v>
       </c>
       <c r="E23" s="4"/>
     </row>
@@ -953,7 +969,7 @@
         <v>51111010</v>
       </c>
       <c r="D24" s="4">
-        <v>163.0</v>
+        <v>120.0</v>
       </c>
       <c r="E24" s="4"/>
     </row>
@@ -967,9 +983,7 @@
       <c r="C25" s="3">
         <v>51111010</v>
       </c>
-      <c r="D25" s="4">
-        <v>666.61</v>
-      </c>
+      <c r="D25" s="4"/>
       <c r="E25" s="4"/>
     </row>
     <row r="26" spans="1:5">
@@ -983,7 +997,7 @@
         <v>51111010</v>
       </c>
       <c r="D26" s="4">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="E26" s="4"/>
     </row>
@@ -998,7 +1012,7 @@
         <v>51141009</v>
       </c>
       <c r="D27" s="4">
-        <v>70.0</v>
+        <v>10.0</v>
       </c>
       <c r="E27" s="4"/>
     </row>
@@ -1064,9 +1078,7 @@
       <c r="C32" s="3">
         <v>51141009</v>
       </c>
-      <c r="D32" s="4">
-        <v>347.5</v>
-      </c>
+      <c r="D32" s="4"/>
       <c r="E32" s="4"/>
     </row>
     <row r="33" spans="1:5">
@@ -1079,7 +1091,9 @@
       <c r="C33" s="3">
         <v>51111010</v>
       </c>
-      <c r="D33" s="4"/>
+      <c r="D33" s="4">
+        <v>150.0</v>
+      </c>
       <c r="E33" s="4"/>
     </row>
     <row r="34" spans="1:5">
@@ -1092,7 +1106,9 @@
       <c r="C34" s="3">
         <v>51111010</v>
       </c>
-      <c r="D34" s="4"/>
+      <c r="D34" s="4">
+        <v>50.0</v>
+      </c>
       <c r="E34" s="4"/>
     </row>
     <row r="35" spans="1:5">
@@ -1105,7 +1121,9 @@
       <c r="C35" s="3">
         <v>51111010</v>
       </c>
-      <c r="D35" s="4"/>
+      <c r="D35" s="4">
+        <v>10.0</v>
+      </c>
       <c r="E35" s="4"/>
     </row>
     <row r="36" spans="1:5">
@@ -1118,7 +1136,9 @@
       <c r="C36" s="3">
         <v>51141004</v>
       </c>
-      <c r="D36" s="4"/>
+      <c r="D36" s="4">
+        <v>8.26</v>
+      </c>
       <c r="E36" s="4"/>
     </row>
     <row r="37" spans="1:5">
@@ -1157,7 +1177,9 @@
       <c r="C39" s="3">
         <v>51111010</v>
       </c>
-      <c r="D39" s="4"/>
+      <c r="D39" s="4">
+        <v>1.0</v>
+      </c>
       <c r="E39" s="4"/>
     </row>
     <row r="40" spans="1:5">
@@ -1248,7 +1270,9 @@
       <c r="C46" s="3">
         <v>51114007</v>
       </c>
-      <c r="D46" s="4"/>
+      <c r="D46" s="4">
+        <v>88.91</v>
+      </c>
       <c r="E46" s="4"/>
     </row>
     <row r="47" spans="1:5">
@@ -1262,7 +1286,7 @@
         <v>51114007</v>
       </c>
       <c r="D47" s="4">
-        <v>302.11</v>
+        <v>178.3</v>
       </c>
       <c r="E47" s="4"/>
     </row>
@@ -1290,7 +1314,7 @@
         <v>51171004</v>
       </c>
       <c r="D49" s="4">
-        <v>400.0</v>
+        <v>200.0</v>
       </c>
       <c r="E49" s="4"/>
     </row>
@@ -1320,8 +1344,8 @@
         <v>51171011</v>
       </c>
       <c r="D51" s="4"/>
-      <c r="E51" s="4" t="s">
-        <v>53</v>
+      <c r="E51" s="4">
+        <v>500.0</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1329,7 +1353,7 @@
         <v>47</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C52" s="3">
         <v>51121002</v>
@@ -1342,14 +1366,14 @@
         <v>48</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4">
-        <v>700.0</v>
+        <v>350.0</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1357,14 +1381,14 @@
         <v>49</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C54" s="3">
         <v>20501024</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4">
-        <v>302.11</v>
+        <v>267.21</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1372,14 +1396,14 @@
         <v>50</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="4"/>
+      <c r="E55" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4">
-        <v>616.75</v>
       </c>
     </row>
     <row r="56" spans="1:5">

--- a/e2e/expectedData/moju_Expat_Local.xlsx
+++ b/e2e/expectedData/moju_Expat_Local.xlsx
@@ -80,7 +80,7 @@
     <t>Basic Salary - Expat</t>
   </si>
   <si>
-    <t>1,830.00</t>
+    <t>1,710.00</t>
   </si>
   <si>
     <t>Position Allowance - Expat</t>
@@ -170,12 +170,15 @@
     <t>Potongan Karyawan</t>
   </si>
   <si>
-    <t>1,130.00</t>
+    <t>2,450.00</t>
   </si>
   <si>
     <t>Potongan Donasi THR</t>
   </si>
   <si>
+    <t>1,000.00</t>
+  </si>
+  <si>
     <t>Potongan Biaya Housing</t>
   </si>
   <si>
@@ -194,16 +197,13 @@
     <t>TL20000002</t>
   </si>
   <si>
-    <t>2,737.72</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>4,984.93</t>
-  </si>
-  <si>
-    <t>DILI, 09 September 2026</t>
+    <t>5,277.93</t>
+  </si>
+  <si>
+    <t>DILI, 10 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -909,7 +909,7 @@
         <v>51111010</v>
       </c>
       <c r="D20" s="4">
-        <v>230.0</v>
+        <v>220.0</v>
       </c>
       <c r="E20" s="4"/>
     </row>
@@ -924,7 +924,7 @@
         <v>51111010</v>
       </c>
       <c r="D21" s="4">
-        <v>100.0</v>
+        <v>50.0</v>
       </c>
       <c r="E21" s="4"/>
     </row>
@@ -954,7 +954,7 @@
         <v>51141004</v>
       </c>
       <c r="D23" s="4">
-        <v>59.38</v>
+        <v>13.94</v>
       </c>
       <c r="E23" s="4"/>
     </row>
@@ -968,9 +968,7 @@
       <c r="C24" s="3">
         <v>51111010</v>
       </c>
-      <c r="D24" s="4">
-        <v>120.0</v>
-      </c>
+      <c r="D24" s="4"/>
       <c r="E24" s="4"/>
     </row>
     <row r="25" spans="1:5">
@@ -997,7 +995,7 @@
         <v>51111010</v>
       </c>
       <c r="D26" s="4">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="E26" s="4"/>
     </row>
@@ -1011,9 +1009,7 @@
       <c r="C27" s="3">
         <v>51141009</v>
       </c>
-      <c r="D27" s="4">
-        <v>10.0</v>
-      </c>
+      <c r="D27" s="4"/>
       <c r="E27" s="4"/>
     </row>
     <row r="28" spans="1:5">
@@ -1092,7 +1088,7 @@
         <v>51111010</v>
       </c>
       <c r="D33" s="4">
-        <v>150.0</v>
+        <v>270.0</v>
       </c>
       <c r="E33" s="4"/>
     </row>
@@ -1107,7 +1103,7 @@
         <v>51111010</v>
       </c>
       <c r="D34" s="4">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="E34" s="4"/>
     </row>
@@ -1122,7 +1118,7 @@
         <v>51111010</v>
       </c>
       <c r="D35" s="4">
-        <v>10.0</v>
+        <v>60.0</v>
       </c>
       <c r="E35" s="4"/>
     </row>
@@ -1137,7 +1133,7 @@
         <v>51141004</v>
       </c>
       <c r="D36" s="4">
-        <v>8.26</v>
+        <v>53.7</v>
       </c>
       <c r="E36" s="4"/>
     </row>
@@ -1151,7 +1147,9 @@
       <c r="C37" s="3">
         <v>51111010</v>
       </c>
-      <c r="D37" s="4"/>
+      <c r="D37" s="4">
+        <v>120.0</v>
+      </c>
       <c r="E37" s="4"/>
     </row>
     <row r="38" spans="1:5">
@@ -1178,7 +1176,7 @@
         <v>51111010</v>
       </c>
       <c r="D39" s="4">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E39" s="4"/>
     </row>
@@ -1192,7 +1190,9 @@
       <c r="C40" s="3">
         <v>51141009</v>
       </c>
-      <c r="D40" s="4"/>
+      <c r="D40" s="4">
+        <v>10.0</v>
+      </c>
       <c r="E40" s="4"/>
     </row>
     <row r="41" spans="1:5">
@@ -1314,7 +1314,7 @@
         <v>51171004</v>
       </c>
       <c r="D49" s="4">
-        <v>200.0</v>
+        <v>493.0</v>
       </c>
       <c r="E49" s="4"/>
     </row>
@@ -1344,8 +1344,8 @@
         <v>51171011</v>
       </c>
       <c r="D51" s="4"/>
-      <c r="E51" s="4">
-        <v>500.0</v>
+      <c r="E51" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1353,7 +1353,7 @@
         <v>47</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C52" s="3">
         <v>51121002</v>
@@ -1366,14 +1366,14 @@
         <v>48</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4">
-        <v>350.0</v>
+        <v>855.0</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1381,7 +1381,7 @@
         <v>49</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C54" s="3">
         <v>20501024</v>
@@ -1396,14 +1396,14 @@
         <v>50</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D55" s="4"/>
-      <c r="E55" s="4" t="s">
-        <v>59</v>
+      <c r="E55" s="4">
+        <v>705.72</v>
       </c>
     </row>
     <row r="56" spans="1:5">
